--- a/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>HRL</t>
   </si>
@@ -656,198 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E7" s="2">
         <v>44864</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44129</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43765</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43401</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43037</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42673</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42302</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41938</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41574</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41210</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40846</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12110000</v>
+      </c>
+      <c r="E8" s="3">
         <v>12458800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11386200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9608500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9497300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9545700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9167500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9523200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9263900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9316300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8751700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8230700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7895100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10110200</v>
+      </c>
+      <c r="E9" s="3">
         <v>10294100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9458300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7782500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7612700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7566200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14335200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7365000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7455300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7751300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7338800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6898800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6561000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1999800</v>
+      </c>
+      <c r="E10" s="3">
         <v>2164700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1927900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1826000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1884600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1979500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-5167700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2158200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1808600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1565000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1412800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1331900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1334100</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,31 +876,32 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E12" s="3">
         <v>34700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34200</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -905,9 +918,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,38 +963,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>28400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>17300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>21500</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -989,9 +1008,12 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,9 +1053,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1072,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11038000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11146200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10263600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8508200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8301100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8365700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7890800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8199300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8196500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8384600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7945700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7466000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7152800</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1072000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1312600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1122600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1100200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1196300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1180000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1276700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1323900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1067300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>931600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>806000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>764700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>742300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1149,218 +1181,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E20" s="3">
         <v>28000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>46900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>35600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>31500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>27800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1340200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1603400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1397900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1341600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1393000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1369600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1422300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1462100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1203700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1064900</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>890700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>865700</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E22" s="3">
         <v>62500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>43300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>22700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1013500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1278100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1126200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1114700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1209700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1181300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1278600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1317200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1057100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>922200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>798500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>758300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>718800</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>220600</v>
+      </c>
+      <c r="E24" s="3">
         <v>277900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>217000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>206400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>230600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>241600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>431500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>426700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>369900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>316100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>268400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>253400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>239600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,93 +1448,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>792900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1000200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>909100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>908400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>979100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>939700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>847100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>890500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>687300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>606000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>530100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>505000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>479200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>793600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1000000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>908800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>908100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>978800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>939200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>846700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>890100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>686100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>602700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>526200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>474200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,11 +1604,11 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>72900</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1565,12 +1625,15 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1718,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-46900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-35600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-31500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-27800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>793600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1000000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>908800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>908100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>978800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1012100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>846700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>890100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>686100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>602700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>526200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>474200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1853,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>793600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1000000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>908800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>908100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>978800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1012100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>846700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>890100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>686100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>602700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>526200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>474200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E38" s="2">
         <v>44864</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44500</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44129</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43765</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43401</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43037</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42673</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42302</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41938</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41574</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41210</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40846</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,67 +1989,71 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>736500</v>
+      </c>
+      <c r="E41" s="3">
         <v>982100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>613500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1714300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>672900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>459100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>444100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>415100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>347200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>334200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>434000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>682400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>463100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E42" s="3">
         <v>16100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14700</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -1978,312 +2067,336 @@
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>77400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>76100</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>824600</v>
+      </c>
+      <c r="E43" s="3">
         <v>874800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>904000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>743900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>594300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>604400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>640700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>609600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>611800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1244700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>551500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>523500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>485500</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1680400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1716100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1369200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1072800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1042400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>963500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>921000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>985700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>993300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1054600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>968000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>950500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>885800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E45" s="3">
         <v>48000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>110700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>107900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>93900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>86900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>87700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3297200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3637100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2947800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3579100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2361400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2050100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2026500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2029900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2063000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2132800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2047400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2320700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1998200</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>725100</v>
+      </c>
+      <c r="E47" s="3">
         <v>271100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>299000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>308400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>289200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>273200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>242400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>239600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>259000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>264500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>270600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>286500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>295700</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2297700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2214800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2181400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1951300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1629100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1512600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1203300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1105400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1011700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1001800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>955300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>924500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>907100</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6685600</v>
+      </c>
+      <c r="E49" s="3">
         <v>6728900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6751400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3689000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3515500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3921300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3146800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2737800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2526700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1781300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1312600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>753900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>762900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,51 +2481,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>443000</v>
+      </c>
+      <c r="E52" s="3">
         <v>455100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>516700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>380500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>313800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>385100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>356900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>257400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>279400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>275300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>330000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>278300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>280400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,51 +2571,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13448800</v>
+      </c>
+      <c r="E54" s="3">
         <v>13306900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12696300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9908300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8109000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8142300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6975900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6370100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6139800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5455600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4915900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4564000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4244400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,64 +2657,68 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>771400</v>
+      </c>
+      <c r="E57" s="3">
         <v>816600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>793300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>644600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>587200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>618800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>552700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>481800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>495300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>484000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>387300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>385900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>390200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8800</v>
+        <v>950500</v>
       </c>
       <c r="E58" s="3">
         <v>8800</v>
       </c>
       <c r="F58" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G58" s="3">
         <v>258700</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>8</v>
@@ -2593,14 +2726,14 @@
       <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>185000</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -2608,116 +2741,125 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>589900</v>
+      </c>
+      <c r="E59" s="3">
         <v>647900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>613600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>517800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>520100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>505500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>571400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>533700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>470600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>396700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>388000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2311800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1473300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1415700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1504000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1105000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1138900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1058200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1053200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1214000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>954700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>784000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>786300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>778200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2358700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3290500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3315100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1044900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>250000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>624800</v>
-      </c>
-      <c r="I61" s="3">
-        <v>250000</v>
       </c>
       <c r="J61" s="3">
         <v>250000</v>
@@ -2737,51 +2879,57 @@
       <c r="O61" s="3">
         <v>250000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>250000</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1039300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1002900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>987200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>929100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>828400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>773700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>728000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>615500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>674400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>638900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>565300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>702700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>556400</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,51 +3059,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5713900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5771600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5723400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3482700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2187500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2541500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2040000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1922100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2141600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1849900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1604800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1744500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1587800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,51 +3303,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7493000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7313400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6881900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6523300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6128200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5730000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5162600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4736600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4216100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3805700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3452500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3135300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2824300</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,51 +3483,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7734900</v>
+      </c>
+      <c r="E76" s="3">
         <v>7535300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6972900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6425500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5921500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5600800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4935900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4448000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3998200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3605700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3311000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2819500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2656600</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3573,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E80" s="2">
         <v>44864</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44500</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44129</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43765</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43401</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43037</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42673</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42302</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41938</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41574</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41210</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40846</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>793600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1000000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>908800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>908100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>978800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1012100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>846700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>890100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>686100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>602700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>526200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>474200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,50 +3690,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>253300</v>
+      </c>
+      <c r="E83" s="3">
         <v>262800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>228400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>205800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>165200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>161900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>131000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>132000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>133400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>130000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>119500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>124200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,51 +3957,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1047800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1135000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1001900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1128000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>923000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1241700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1033900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>992800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>992000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>746900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>637800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>517800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>490500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,50 +4024,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-270200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-278900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-232400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-367500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-293800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-389600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-221300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-255500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-144100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-159100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-106800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-132300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-96900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,51 +4156,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-689500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-258000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3625800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-656300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>220200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1235400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-587200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-409000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-616800</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-106800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-171000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,50 +4223,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-592900</v>
+      </c>
+      <c r="E96" s="3">
         <v>-557800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-523100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-487400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-437100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-388100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-346000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-296500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-250800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-203200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-174300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-152200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-130000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,133 +4400,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-486700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1520500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>566200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-926200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>11600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-418800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-509600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-70600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-229400</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-192700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-325500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-245600</v>
+      </c>
+      <c r="E102" s="3">
         <v>368600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1100800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1041400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>213800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>67900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-99800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-248400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>219300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>HRL</t>
   </si>
@@ -656,210 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E7" s="2">
         <v>45228</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44864</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44500</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44129</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43765</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43401</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43037</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42673</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42302</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41938</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41574</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41210</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40846</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11920800</v>
+      </c>
+      <c r="E8" s="3">
         <v>12110000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12458800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11386200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9608500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9497300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9545700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9167500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9523200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9263900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9316300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8751700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8230700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7895100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9898700</v>
+      </c>
+      <c r="E9" s="3">
         <v>10110200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10294100</v>
       </c>
-      <c r="F9" s="3">
-        <v>9458300</v>
-      </c>
       <c r="G9" s="3">
+        <v>9445400</v>
+      </c>
+      <c r="H9" s="3">
         <v>7782500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7612700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7566200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14335200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7365000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7455300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7751300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7338800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6898800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6561000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2022100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1999800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2164700</v>
       </c>
-      <c r="F10" s="3">
-        <v>1927900</v>
-      </c>
       <c r="G10" s="3">
+        <v>1940800</v>
+      </c>
+      <c r="H10" s="3">
         <v>1826000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1884600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1979500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-5167700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2158200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1808600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1565000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1412800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1331900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1334100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -877,34 +889,35 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E12" s="3">
         <v>33700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34200</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -921,9 +934,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,41 +982,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E14" s="3">
         <v>28400</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>43200</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="J14" s="3">
         <v>17300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>21500</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1011,32 +1030,35 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>257800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>253300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>235900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>209300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>205800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>165200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>161900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1056,9 +1078,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1073,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11038000</v>
+        <v>10875200</v>
       </c>
       <c r="E17" s="3">
-        <v>11146200</v>
+        <v>11052300</v>
       </c>
       <c r="F17" s="3">
-        <v>10263600</v>
+        <v>11173400</v>
       </c>
       <c r="G17" s="3">
-        <v>8508200</v>
+        <v>10268200</v>
       </c>
       <c r="H17" s="3">
-        <v>8301100</v>
+        <v>8543800</v>
       </c>
       <c r="I17" s="3">
-        <v>8365700</v>
+        <v>8356800</v>
       </c>
       <c r="J17" s="3">
+        <v>8407400</v>
+      </c>
+      <c r="K17" s="3">
         <v>7890800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8199300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8196500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8384600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7945700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7466000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7152800</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1072000</v>
+        <v>1045600</v>
       </c>
       <c r="E18" s="3">
-        <v>1312600</v>
+        <v>1057700</v>
       </c>
       <c r="F18" s="3">
-        <v>1122600</v>
+        <v>1285400</v>
       </c>
       <c r="G18" s="3">
-        <v>1100200</v>
+        <v>1118000</v>
       </c>
       <c r="H18" s="3">
-        <v>1196300</v>
+        <v>1064600</v>
       </c>
       <c r="I18" s="3">
-        <v>1180000</v>
+        <v>1140600</v>
       </c>
       <c r="J18" s="3">
+        <v>1138300</v>
+      </c>
+      <c r="K18" s="3">
         <v>1276700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1323900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1067300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>931600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>806000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>764700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>742300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1182,233 +1214,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>14800</v>
+        <v>-51100</v>
       </c>
       <c r="E20" s="3">
-        <v>28000</v>
+        <v>-42800</v>
       </c>
       <c r="F20" s="3">
-        <v>46900</v>
+        <v>-27200</v>
       </c>
       <c r="G20" s="3">
-        <v>35600</v>
+        <v>-47800</v>
       </c>
       <c r="H20" s="3">
-        <v>31500</v>
+        <v>-35600</v>
       </c>
       <c r="I20" s="3">
-        <v>27800</v>
+        <v>-39200</v>
       </c>
       <c r="J20" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="K20" s="3">
         <v>14600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1340200</v>
+        <v>1354400</v>
       </c>
       <c r="E21" s="3">
-        <v>1603400</v>
+        <v>1353700</v>
       </c>
       <c r="F21" s="3">
-        <v>1397900</v>
+        <v>1548500</v>
       </c>
       <c r="G21" s="3">
-        <v>1341600</v>
+        <v>1375100</v>
       </c>
       <c r="H21" s="3">
-        <v>1393000</v>
+        <v>1306000</v>
       </c>
       <c r="I21" s="3">
-        <v>1369600</v>
+        <v>1345000</v>
       </c>
       <c r="J21" s="3">
+        <v>1359100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1422300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1462100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1203700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1064900</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>890700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>865700</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>80900</v>
+      </c>
+      <c r="E22" s="3">
         <v>73400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>62500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>43300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>21100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>22700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1035400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1013500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1278100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1126200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1114700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1209700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1181300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1278600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1317200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1057100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>922200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>798500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>758300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>718800</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>230800</v>
+      </c>
+      <c r="E24" s="3">
         <v>220600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>277900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>217000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>206400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>230600</v>
       </c>
-      <c r="I24" s="3">
-        <v>241600</v>
-      </c>
       <c r="J24" s="3">
+        <v>168700</v>
+      </c>
+      <c r="K24" s="3">
         <v>431500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>426700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>369900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>316100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>268400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>253400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>239600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1451,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>804600</v>
+      </c>
+      <c r="E26" s="3">
         <v>792900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1000200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>909100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>908400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>979100</v>
       </c>
-      <c r="I26" s="3">
-        <v>939700</v>
-      </c>
       <c r="J26" s="3">
+        <v>1012600</v>
+      </c>
+      <c r="K26" s="3">
         <v>847100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>890500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>687300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>606000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>530100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>505000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>479200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E27" s="3">
         <v>793600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1000000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>908800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>908100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>978800</v>
       </c>
-      <c r="I27" s="3">
-        <v>939200</v>
-      </c>
       <c r="J27" s="3">
+        <v>1012100</v>
+      </c>
+      <c r="K27" s="3">
         <v>846700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>890100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>686100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>602700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>526200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>474200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1586,32 +1643,35 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>72900</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1628,12 +1688,15 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1676,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1721,99 +1787,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-14800</v>
+        <v>51100</v>
       </c>
       <c r="E32" s="3">
-        <v>-28000</v>
+        <v>42800</v>
       </c>
       <c r="F32" s="3">
-        <v>-46900</v>
+        <v>27200</v>
       </c>
       <c r="G32" s="3">
-        <v>-35600</v>
+        <v>47800</v>
       </c>
       <c r="H32" s="3">
-        <v>-31500</v>
+        <v>35600</v>
       </c>
       <c r="I32" s="3">
-        <v>-27800</v>
+        <v>39200</v>
       </c>
       <c r="J32" s="3">
+        <v>59000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E33" s="3">
         <v>793600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1000000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>908800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>908100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>978800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1012100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>846700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>890100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>686100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>602700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>526200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>474200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1856,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E35" s="3">
         <v>793600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1000000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>908800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>908100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>978800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1012100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>846700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>890100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>686100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>602700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>526200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>474200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E38" s="2">
         <v>45228</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44864</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44500</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44129</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43765</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43401</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43037</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42673</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42302</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41938</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41574</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41210</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40846</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1971,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1990,76 +2075,80 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>741900</v>
+      </c>
+      <c r="E41" s="3">
         <v>736500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>982100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>613500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1714300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>672900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>459100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>444100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>415100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>347200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>334200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>434000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>682400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>463100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E42" s="3">
         <v>16700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14700</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -2070,333 +2159,357 @@
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>77400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>76100</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>868300</v>
+      </c>
+      <c r="E43" s="3">
         <v>824600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>874800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>904000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>743900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>594300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>604400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>640700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>609600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>611800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1244700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>551500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>523500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>485500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1576300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1680400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1716100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1369200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1072800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1042400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>963500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>921000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>985700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>993300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1054600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>968000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>950500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>885800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>39000</v>
+        <v>9900</v>
       </c>
       <c r="E45" s="3">
-        <v>48000</v>
+        <v>13800</v>
       </c>
       <c r="F45" s="3">
-        <v>39900</v>
+        <v>12400</v>
       </c>
       <c r="G45" s="3">
-        <v>30800</v>
+        <v>13500</v>
       </c>
       <c r="H45" s="3">
-        <v>37100</v>
+        <v>12400</v>
       </c>
       <c r="I45" s="3">
-        <v>23000</v>
+        <v>14500</v>
       </c>
       <c r="J45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K45" s="3">
         <v>20700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>110700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>107900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>93900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>86900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>87700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3246500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3297200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3637100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2947800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3579100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2361400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2050100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2026500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2029900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2063000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2132800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2047400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2320700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1998200</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>719500</v>
+      </c>
+      <c r="E47" s="3">
         <v>725100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>271100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>299000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>308400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>289200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>273200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>242400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>239600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>259000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>264500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>270600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>286500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>295700</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2342400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2297700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2214800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2181400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1951300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1629100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1512600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1203300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1105400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1011700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1001800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>955300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>924500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>907100</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6656200</v>
+      </c>
+      <c r="E49" s="3">
         <v>6685600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6728900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6751400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3689000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3515500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3921300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3146800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2737800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2526700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1781300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1312600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>753900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>762900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2439,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2484,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>470200</v>
+      </c>
+      <c r="E52" s="3">
         <v>443000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>455100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>516700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>380500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>313800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>385100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>356900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>257400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>279400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>275300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>330000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>278300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>280400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2574,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13434700</v>
+      </c>
+      <c r="E54" s="3">
         <v>13448800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13306900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12696300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9908300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8109000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8142300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6975900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6370100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6139800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5455600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4915900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4564000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4244400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2639,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2658,85 +2787,89 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>735600</v>
+      </c>
+      <c r="E57" s="3">
         <v>771400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>816600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>793300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>644600</v>
       </c>
-      <c r="H57" s="3">
-        <v>587200</v>
-      </c>
       <c r="I57" s="3">
+        <v>590000</v>
+      </c>
+      <c r="J57" s="3">
         <v>618800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>552700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>481800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>495300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>484000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>387300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>385900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>390200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>950500</v>
+        <v>39900</v>
       </c>
       <c r="E58" s="3">
-        <v>8800</v>
+        <v>976800</v>
       </c>
       <c r="F58" s="3">
-        <v>8800</v>
+        <v>30000</v>
       </c>
       <c r="G58" s="3">
-        <v>258700</v>
-      </c>
-      <c r="H58" s="3" t="s">
+        <v>27100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>270700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>185000</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -2744,125 +2877,134 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>589900</v>
+        <v>21900</v>
       </c>
       <c r="E59" s="3">
-        <v>647900</v>
+        <v>15200</v>
       </c>
       <c r="F59" s="3">
-        <v>613600</v>
+        <v>32900</v>
       </c>
       <c r="G59" s="3">
-        <v>600700</v>
+        <v>23500</v>
       </c>
       <c r="H59" s="3">
-        <v>517800</v>
+        <v>22500</v>
       </c>
       <c r="I59" s="3">
-        <v>520100</v>
+        <v>6200</v>
       </c>
       <c r="J59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K59" s="3">
         <v>505500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>571400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>533700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>470600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>396700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>388000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1399300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2311800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1473300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1415700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1504000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1105000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1138900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1058200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1053200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1214000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>954700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>784000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>786300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>778200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2358700</v>
+        <v>2972200</v>
       </c>
       <c r="E61" s="3">
-        <v>3290500</v>
+        <v>2468000</v>
       </c>
       <c r="F61" s="3">
-        <v>3315100</v>
+        <v>3346100</v>
       </c>
       <c r="G61" s="3">
-        <v>1044900</v>
+        <v>3371900</v>
       </c>
       <c r="H61" s="3">
+        <v>1088100</v>
+      </c>
+      <c r="I61" s="3">
         <v>250000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>624800</v>
-      </c>
-      <c r="J61" s="3">
-        <v>250000</v>
       </c>
       <c r="K61" s="3">
         <v>250000</v>
@@ -2882,54 +3024,60 @@
       <c r="P61" s="3">
         <v>250000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>250000</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1039300</v>
+        <v>89900</v>
       </c>
       <c r="E62" s="3">
-        <v>1002900</v>
+        <v>82700</v>
       </c>
       <c r="F62" s="3">
-        <v>987200</v>
+        <v>86300</v>
       </c>
       <c r="G62" s="3">
-        <v>929100</v>
+        <v>105800</v>
       </c>
       <c r="H62" s="3">
-        <v>828400</v>
+        <v>114300</v>
       </c>
       <c r="I62" s="3">
-        <v>773700</v>
+        <v>115400</v>
       </c>
       <c r="J62" s="3">
+        <v>99100</v>
+      </c>
+      <c r="K62" s="3">
         <v>728000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>615500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>674400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>638900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>565300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>702700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>556400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2972,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3017,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3062,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5713900</v>
+        <v>5430700</v>
       </c>
       <c r="E66" s="3">
-        <v>5771600</v>
+        <v>5709800</v>
       </c>
       <c r="F66" s="3">
-        <v>5723400</v>
+        <v>5766700</v>
       </c>
       <c r="G66" s="3">
-        <v>3482700</v>
+        <v>5718000</v>
       </c>
       <c r="H66" s="3">
-        <v>2187500</v>
+        <v>3478000</v>
       </c>
       <c r="I66" s="3">
-        <v>2541500</v>
+        <v>2183500</v>
       </c>
       <c r="J66" s="3">
+        <v>2537500</v>
+      </c>
+      <c r="K66" s="3">
         <v>2040000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1922100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2141600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1849900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1604800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1744500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1587800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3127,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3171,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3216,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3261,9 +3428,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3306,54 +3476,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7677500</v>
+      </c>
+      <c r="E72" s="3">
         <v>7493000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7313400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6881900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6523300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6128200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5730000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5162600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4736600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4216100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3805700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3452500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3135300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2824300</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3396,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3441,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3486,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7993400</v>
+      </c>
+      <c r="E76" s="3">
         <v>7734900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7535300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6972900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6425500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5921500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5600800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4935900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4448000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3998200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3605700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3311000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2819500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2656600</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3576,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E80" s="2">
         <v>45228</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44864</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44500</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44129</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43765</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43401</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43037</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42673</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42302</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41938</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41574</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41210</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40846</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E81" s="3">
         <v>793600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1000000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>908800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>908100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>978800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1012100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>846700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>890100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>686100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>602700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>526200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>474200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3691,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>253300</v>
+        <v>233800</v>
       </c>
       <c r="E83" s="3">
-        <v>262800</v>
+        <v>227300</v>
       </c>
       <c r="F83" s="3">
-        <v>228400</v>
+        <v>213000</v>
       </c>
       <c r="G83" s="3">
-        <v>205800</v>
+        <v>183800</v>
       </c>
       <c r="H83" s="3">
-        <v>165200</v>
+        <v>165700</v>
       </c>
       <c r="I83" s="3">
-        <v>161900</v>
+        <v>153200</v>
       </c>
       <c r="J83" s="3">
+        <v>149200</v>
+      </c>
+      <c r="K83" s="3">
         <v>131000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>132000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>133400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>130000</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>119500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>124200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3780,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3825,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3870,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3915,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3960,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1266700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1047800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1135000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1001900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1128000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>923000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1241700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1033900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>992800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>992000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>746900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>637800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>517800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>490500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4025,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-256400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-270200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-278900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-232400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-367500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-293800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-389600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-221300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-255500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-144100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-159100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-106800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-132300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-96900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4114,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4159,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-236900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-689500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-258000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3625800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-656300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>220200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1235400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-587200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-409000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-616800</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-106800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-171000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4224,53 +4456,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-592900</v>
+        <v>615000</v>
       </c>
       <c r="E96" s="3">
-        <v>-557800</v>
+        <v>592900</v>
       </c>
       <c r="F96" s="3">
-        <v>-523100</v>
+        <v>557800</v>
       </c>
       <c r="G96" s="3">
-        <v>-487400</v>
+        <v>523100</v>
       </c>
       <c r="H96" s="3">
-        <v>-437100</v>
+        <v>487400</v>
       </c>
       <c r="I96" s="3">
-        <v>-388100</v>
+        <v>437100</v>
       </c>
       <c r="J96" s="3">
+        <v>388100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-346000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-296500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-250800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-203200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-174300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-152200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-130000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4313,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4358,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4403,142 +4645,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1030100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-486700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1520500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>566200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-926200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>11600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-418800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-509600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-70600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-229400</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-192700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-325500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-21700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-245600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>368600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1100800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1041400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>213800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>67900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-99800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-248400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>219300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
@@ -780,10 +780,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9898700</v>
+        <v>9893100</v>
       </c>
       <c r="E9" s="3">
-        <v>10110200</v>
+        <v>10109200</v>
       </c>
       <c r="F9" s="3">
         <v>10294100</v>
@@ -828,10 +828,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2022100</v>
+        <v>2027700</v>
       </c>
       <c r="E10" s="3">
-        <v>1999800</v>
+        <v>2000800</v>
       </c>
       <c r="F10" s="3">
         <v>2164700</v>
@@ -992,10 +992,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>28800</v>
+        <v>81800</v>
       </c>
       <c r="E14" s="3">
-        <v>28400</v>
+        <v>37700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1105,10 +1105,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10875200</v>
+        <v>10822200</v>
       </c>
       <c r="E17" s="3">
-        <v>11052300</v>
+        <v>11043000</v>
       </c>
       <c r="F17" s="3">
         <v>11173400</v>
@@ -1153,10 +1153,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1045600</v>
+        <v>1098600</v>
       </c>
       <c r="E18" s="3">
-        <v>1057700</v>
+        <v>1067000</v>
       </c>
       <c r="F18" s="3">
         <v>1285400</v>
@@ -1269,10 +1269,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1354400</v>
+        <v>1407500</v>
       </c>
       <c r="E21" s="3">
-        <v>1353700</v>
+        <v>1363100</v>
       </c>
       <c r="F21" s="3">
         <v>1548500</v>
@@ -2274,10 +2274,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>9900</v>
+        <v>8100</v>
       </c>
       <c r="E45" s="3">
-        <v>13800</v>
+        <v>19000</v>
       </c>
       <c r="F45" s="3">
         <v>12400</v>

--- a/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HRL_YR_FIN.xlsx
@@ -656,222 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45956</v>
+      </c>
+      <c r="E7" s="2">
         <v>45592</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45228</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44864</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44500</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44129</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43765</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43401</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43037</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42673</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42302</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41938</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41574</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41210</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40846</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12106200</v>
+      </c>
+      <c r="E8" s="3">
         <v>11920800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12110000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12458800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11386200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9608500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9497300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9545700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9167500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9523200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9263900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9316300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8751700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8230700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7895100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10205000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9893100</v>
       </c>
-      <c r="E9" s="3">
-        <v>10109200</v>
-      </c>
       <c r="F9" s="3">
+        <v>10110200</v>
+      </c>
+      <c r="G9" s="3">
         <v>10294100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9445400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7782500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7612700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7566200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14335200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7365000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7455300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7751300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7338800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6898800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6561000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1901200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2027700</v>
       </c>
-      <c r="E10" s="3">
-        <v>2000800</v>
-      </c>
       <c r="F10" s="3">
+        <v>1999800</v>
+      </c>
+      <c r="G10" s="3">
         <v>2164700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1940800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1826000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1884600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1979500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-5167700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2158200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1808600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1565000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1412800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1331900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1334100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,37 +902,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E12" s="3">
         <v>36100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>33600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34200</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -937,9 +950,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,44 +1001,47 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>81800</v>
+        <v>148900</v>
       </c>
       <c r="E14" s="3">
-        <v>37700</v>
-      </c>
-      <c r="F14" s="3" t="s">
+        <v>77800</v>
+      </c>
+      <c r="F14" s="3">
+        <v>28400</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>43200</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-16500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>17300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>21500</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1033,36 +1052,39 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>263900</v>
+      </c>
+      <c r="E15" s="3">
         <v>257800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>253300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>235900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>209300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>205800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>165200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>161900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1081,9 +1103,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10822200</v>
+        <v>11145500</v>
       </c>
       <c r="E17" s="3">
-        <v>11043000</v>
+        <v>10826100</v>
       </c>
       <c r="F17" s="3">
+        <v>11052300</v>
+      </c>
+      <c r="G17" s="3">
         <v>11173400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10268200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8543800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8356800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8407400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7890800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8199300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8196500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8384600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7945700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7466000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7152800</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1098600</v>
+        <v>960700</v>
       </c>
       <c r="E18" s="3">
-        <v>1067000</v>
+        <v>1094700</v>
       </c>
       <c r="F18" s="3">
+        <v>1057700</v>
+      </c>
+      <c r="G18" s="3">
         <v>1285400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1118000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1064600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1140600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1138300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1276700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1323900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1067300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>931600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>806000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>764700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>742300</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1215,248 +1247,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-51100</v>
+        <v>94500</v>
       </c>
       <c r="E20" s="3">
-        <v>-42800</v>
+        <v>-59300</v>
       </c>
       <c r="F20" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-27200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-47800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-35600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-39200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-59000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1407500</v>
+        <v>1130100</v>
       </c>
       <c r="E21" s="3">
-        <v>1363100</v>
+        <v>1411800</v>
       </c>
       <c r="F21" s="3">
+        <v>1345100</v>
+      </c>
+      <c r="G21" s="3">
         <v>1548500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1375100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1306000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1345000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1359100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1422300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1462100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1203700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1064900</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>890700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>865700</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E22" s="3">
         <v>80900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>73400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>62500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>43300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>21100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>26500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>22700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>663400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1035400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1013500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1278100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1126200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1114700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1209700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1181300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1278600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1317200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1057100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>922200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>798500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>758300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>718800</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>185700</v>
+      </c>
+      <c r="E24" s="3">
         <v>230800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>220600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>277900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>217000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>206400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>230600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>168700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>431500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>426700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>369900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>316100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>268400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>253400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>239600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>477800</v>
+      </c>
+      <c r="E26" s="3">
         <v>804600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>792900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1000200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>909100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>908400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>979100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1012600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>847100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>890500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>687300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>606000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>530100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>505000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>479200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>478200</v>
+      </c>
+      <c r="E27" s="3">
         <v>805000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>793600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1000000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>908800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>908100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>978800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1012100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>846700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>890100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>686100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>602700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>526200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>474200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1646,9 +1703,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1733,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1691,12 +1751,15 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,105 +1856,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>51100</v>
+        <v>-94500</v>
       </c>
       <c r="E32" s="3">
-        <v>42800</v>
+        <v>59300</v>
       </c>
       <c r="F32" s="3">
+        <v>34100</v>
+      </c>
+      <c r="G32" s="3">
         <v>27200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>47800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>35600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>39200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>59000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>478200</v>
+      </c>
+      <c r="E33" s="3">
         <v>805000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>793600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1000000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>908800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>908100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>978800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1012100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>846700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>890100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>686100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>602700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>526200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>474200</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>478200</v>
+      </c>
+      <c r="E35" s="3">
         <v>805000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>793600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1000000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>908800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>908100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>978800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1012100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>846700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>890100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>686100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>602700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>526200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>474200</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45956</v>
+      </c>
+      <c r="E38" s="2">
         <v>45592</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45228</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44864</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44500</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44129</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43765</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43401</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43037</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42673</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42302</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41938</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41574</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41210</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40846</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,82 +2161,86 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>670700</v>
+      </c>
+      <c r="E41" s="3">
         <v>741900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>736500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>982100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>613500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1714300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>672900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>459100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>444100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>415100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>347200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>334200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>434000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>682400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>463100</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E42" s="3">
         <v>24700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
@@ -2162,354 +2251,378 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>77400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>76100</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>881600</v>
+      </c>
+      <c r="E43" s="3">
         <v>868300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>824600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>874800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>904000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>743900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>594300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>604400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>640700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>609600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>611800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1244700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>551500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>523500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>485500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1747300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1576300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1680400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1716100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1369200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1072800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1042400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>963500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>921000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>985700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>993300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1054600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>968000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>950500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>885800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E45" s="3">
         <v>8100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>110700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>107900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>93900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>86900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>87700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3405700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3246500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3297200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3637100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2947800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3579100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2361400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2050100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2026500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2029900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2063000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2132800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2047400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2320700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1998200</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E47" s="3">
         <v>719500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>725100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>271100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>299000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>308400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>289200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>273200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>242400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>239600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>259000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>264500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>270600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>286500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>295700</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2402100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2342400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2297700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2214800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2181400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1951300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1629100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1512600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1203300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1105400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1011700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1001800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>955300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>924500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>907100</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6571400</v>
+      </c>
+      <c r="E49" s="3">
         <v>6656200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6685600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6728900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6751400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3689000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3515500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3921300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3146800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2737800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2526700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1781300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1312600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>753900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>762900</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E52" s="3">
         <v>470200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>443000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>455100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>516700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>380500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>313800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>385100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>356900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>257400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>279400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>275300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>330000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>278300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>280400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13393100</v>
+      </c>
+      <c r="E54" s="3">
         <v>13434700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13448800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13306900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12696300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9908300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8109000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8142300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6975900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6370100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6139800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5455600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4915900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4564000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4244400</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,91 +2917,95 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>731600</v>
+      </c>
+      <c r="E57" s="3">
         <v>735600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>771400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>816600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>793300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>644600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>590000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>618800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>552700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>481800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>495300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>484000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>387300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>385900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>390200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E58" s="3">
         <v>39900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>976800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>30000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>27100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>270700</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>185000</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -2880,134 +3013,143 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E59" s="3">
         <v>21900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>505500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>571400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>533700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>470600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>396700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>388000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1380800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1399300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2311800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1473300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1415700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1504000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1105000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1138900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1058200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1053200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1214000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>954700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>784000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>786300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>778200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2984000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2972200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2468000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3346100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3371900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1088100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>250000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>624800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>250000</v>
       </c>
       <c r="L61" s="3">
         <v>250000</v>
@@ -3027,57 +3169,63 @@
       <c r="Q61" s="3">
         <v>250000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>250000</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E62" s="3">
         <v>89900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>82700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>86300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>105800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>114300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>115400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>99100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>728000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>615500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>674400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>638900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>565300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>702700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>556400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5477300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5430700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5709800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5766700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5718000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3478000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2183500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2537500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2040000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1922100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2141600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1849900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1604800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1744500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1587800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,9 +3547,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3431,9 +3598,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7516700</v>
+      </c>
+      <c r="E72" s="3">
         <v>7677500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7493000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7313400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6881900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6523300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6128200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5730000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5162600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4736600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4216100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3805700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3452500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3135300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2824300</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7901200</v>
+      </c>
+      <c r="E76" s="3">
         <v>7993400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7734900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7535300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6972900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6425500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5921500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5600800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4935900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4448000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3998200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3605700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3311000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2819500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2656600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45956</v>
+      </c>
+      <c r="E80" s="2">
         <v>45592</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45228</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44864</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44500</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44129</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43765</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43401</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43037</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42673</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42302</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41938</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41574</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41210</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40846</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>478200</v>
+      </c>
+      <c r="E81" s="3">
         <v>805000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>793600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1000000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>908800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>908100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>978800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1012100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>846700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>890100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>686100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>602700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>526200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>474200</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,56 +4086,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>241200</v>
+      </c>
+      <c r="E83" s="3">
         <v>233800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>227300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>213000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>183800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>165700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>153200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>149200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>131000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>132000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>133400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>130000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>119500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>124200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>845300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1266700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1047800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1135000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1001900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1128000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>923000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1241700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1033900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>992800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>992000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>746900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>637800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>517800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>490500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-310900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-256400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-270200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-278900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-232400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-367500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-293800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-389600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-221300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-255500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-144100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-159100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-106800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-132300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-96900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,57 +4614,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-298600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-236900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-689500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-258000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3625800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-656300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>220200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1235400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-587200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-409000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-616800</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-106800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-171000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,56 +4689,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>633200</v>
+      </c>
+      <c r="E96" s="3">
         <v>615000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>592900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>557800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>523100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>487400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>437100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>388100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-346000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-296500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-250800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-203200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-174300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-152200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-130000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,151 +4890,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-614000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1030100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-486700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1520500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>566200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-926200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-418800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-509600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-70600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-229400</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-192700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-325500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E101" s="3">
         <v>5600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-21700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-71200</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-245600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>368600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1100800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1041400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>213800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>29000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>67900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-99800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-248400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>219300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
